--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2017/Aircraft_Cumulative_Statistics_2017.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2017/Aircraft_Cumulative_Statistics_2017.xlsx
@@ -13,75 +13,90 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="40" uniqueCount="40">
   <si>
     <t>Row</t>
   </si>
   <si>
-    <t>Alaska</t>
-  </si>
-  <si>
-    <t>Allegiant</t>
-  </si>
-  <si>
-    <t>American</t>
-  </si>
-  <si>
-    <t>Delta</t>
-  </si>
-  <si>
-    <t>Frontier</t>
-  </si>
-  <si>
-    <t>Hawaiian</t>
-  </si>
-  <si>
-    <t>JetBlue</t>
-  </si>
-  <si>
-    <t>Southwest</t>
-  </si>
-  <si>
-    <t>Spirit</t>
-  </si>
-  <si>
-    <t>Sun Country</t>
-  </si>
-  <si>
-    <t>United</t>
-  </si>
-  <si>
-    <t>CommuteAir</t>
-  </si>
-  <si>
-    <t>Endeavor</t>
-  </si>
-  <si>
-    <t>Envoy</t>
-  </si>
-  <si>
-    <t>GoJet</t>
-  </si>
-  <si>
-    <t>Horizon</t>
-  </si>
-  <si>
-    <t>Mesa</t>
-  </si>
-  <si>
-    <t>Piedmont</t>
-  </si>
-  <si>
-    <t>PSA</t>
-  </si>
-  <si>
-    <t>Republic</t>
-  </si>
-  <si>
-    <t>SkyWest</t>
-  </si>
-  <si>
-    <t>All Airlines</t>
+    <t>E145</t>
+  </si>
+  <si>
+    <t>CRJ-200</t>
+  </si>
+  <si>
+    <t>E170</t>
+  </si>
+  <si>
+    <t>E175</t>
+  </si>
+  <si>
+    <t>CRJ-700</t>
+  </si>
+  <si>
+    <t>E190</t>
+  </si>
+  <si>
+    <t>CRJ-900</t>
+  </si>
+  <si>
+    <t>A319</t>
+  </si>
+  <si>
+    <t>A320</t>
+  </si>
+  <si>
+    <t>A321</t>
+  </si>
+  <si>
+    <t>B717-200</t>
+  </si>
+  <si>
+    <t>B737-700</t>
+  </si>
+  <si>
+    <t>B737-800</t>
+  </si>
+  <si>
+    <t>B737-900</t>
+  </si>
+  <si>
+    <t>B737-900ER</t>
+  </si>
+  <si>
+    <t>B757-200</t>
+  </si>
+  <si>
+    <t>B757-300</t>
+  </si>
+  <si>
+    <t>B767-300</t>
+  </si>
+  <si>
+    <t>B767-400</t>
+  </si>
+  <si>
+    <t>A330-200</t>
+  </si>
+  <si>
+    <t>A330-300</t>
+  </si>
+  <si>
+    <t>A350-900</t>
+  </si>
+  <si>
+    <t>B787-8</t>
+  </si>
+  <si>
+    <t>B787-9</t>
+  </si>
+  <si>
+    <t>B777-200</t>
+  </si>
+  <si>
+    <t>B777-300</t>
+  </si>
+  <si>
+    <t>All Aircraft</t>
   </si>
   <si>
     <t>RPMs</t>
@@ -163,10 +178,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" customWidth="true"/>
+    <col min="1" max="1" width="11.140625" customWidth="true"/>
     <col min="2" max="2" width="15.85546875" customWidth="true"/>
     <col min="3" max="3" width="15.85546875" customWidth="true"/>
     <col min="4" max="4" width="13.140625" customWidth="true"/>
@@ -186,40 +201,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2">
@@ -227,40 +242,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>34672317534</v>
+        <v>2890747483</v>
       </c>
       <c r="C2" s="0">
-        <v>40596407511</v>
+        <v>3765248500</v>
       </c>
       <c r="D2" s="0">
-        <v>770330</v>
+        <v>48026</v>
       </c>
       <c r="E2" s="0">
-        <v>167</v>
+        <v>50</v>
       </c>
       <c r="F2" s="0">
-        <v>185251</v>
+        <v>199282</v>
       </c>
       <c r="G2" s="0">
-        <v>3.52</v>
+        <v>2.54</v>
       </c>
       <c r="H2" s="0">
-        <v>11.470000000000001</v>
+        <v>3.8599999999999999</v>
       </c>
       <c r="I2" s="0">
-        <v>85.409999999999997</v>
+        <v>76.769999999999996</v>
       </c>
       <c r="J2" s="0">
-        <v>1306</v>
+        <v>378</v>
       </c>
       <c r="K2" s="0">
-        <v>3210</v>
+        <v>1013.04</v>
       </c>
       <c r="L2" s="0">
-        <v>19.149999999999999</v>
+        <v>20.260000000000002</v>
       </c>
       <c r="M2" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.082000000000000003</v>
       </c>
     </row>
     <row r="3">
@@ -268,40 +283,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>6966910286</v>
+        <v>6922199171</v>
       </c>
       <c r="C3" s="0">
-        <v>8343419355</v>
+        <v>8832929270</v>
       </c>
       <c r="D3" s="0">
-        <v>507507</v>
+        <v>91476</v>
       </c>
       <c r="E3" s="0">
-        <v>169</v>
+        <v>50</v>
       </c>
       <c r="F3" s="0">
-        <v>54180</v>
+        <v>512122</v>
       </c>
       <c r="G3" s="0">
-        <v>3.2999999999999998</v>
+        <v>5.2999999999999998</v>
       </c>
       <c r="H3" s="0">
-        <v>7.7800000000000002</v>
+        <v>7.5099999999999998</v>
       </c>
       <c r="I3" s="0">
-        <v>83.5</v>
+        <v>78.370000000000005</v>
       </c>
       <c r="J3" s="0">
-        <v>907</v>
+        <v>345</v>
       </c>
       <c r="K3" s="0">
-        <v>3447</v>
+        <v>1343.8800000000001</v>
       </c>
       <c r="L3" s="0">
-        <v>20.329999999999998</v>
+        <v>26.879999999999999</v>
       </c>
       <c r="M3" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="4">
@@ -309,40 +324,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>195786373663</v>
+        <v>3116338885</v>
       </c>
       <c r="C4" s="0">
-        <v>237004283312</v>
+        <v>3972814249</v>
       </c>
       <c r="D4" s="0">
-        <v>724341</v>
+        <v>145738</v>
       </c>
       <c r="E4" s="0">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="F4" s="0">
-        <v>1007799</v>
+        <v>90996</v>
       </c>
       <c r="G4" s="0">
-        <v>3.0800000000000001</v>
+        <v>3.3399999999999999</v>
       </c>
       <c r="H4" s="0">
-        <v>10.039999999999999</v>
+        <v>6.8099999999999996</v>
       </c>
       <c r="I4" s="0">
-        <v>82.609999999999999</v>
+        <v>78.439999999999998</v>
       </c>
       <c r="J4" s="0">
-        <v>1282</v>
+        <v>626</v>
       </c>
       <c r="K4" s="0">
-        <v>4894</v>
+        <v>1351.4400000000001</v>
       </c>
       <c r="L4" s="0">
-        <v>27.440000000000001</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="M4" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="5">
@@ -350,40 +365,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>168236600989</v>
+        <v>20194086472</v>
       </c>
       <c r="C5" s="0">
-        <v>194647878405</v>
+        <v>25399455218</v>
       </c>
       <c r="D5" s="0">
-        <v>813133</v>
+        <v>183509</v>
       </c>
       <c r="E5" s="0">
-        <v>164</v>
+        <v>76</v>
       </c>
       <c r="F5" s="0">
-        <v>762934</v>
+        <v>520291</v>
       </c>
       <c r="G5" s="0">
-        <v>3.1899999999999999</v>
+        <v>3.7599999999999998</v>
       </c>
       <c r="H5" s="0">
-        <v>10.51</v>
+        <v>7.71</v>
       </c>
       <c r="I5" s="0">
-        <v>86.430000000000007</v>
+        <v>79.510000000000005</v>
       </c>
       <c r="J5" s="0">
-        <v>1340</v>
+        <v>643</v>
       </c>
       <c r="K5" s="0">
-        <v>4699</v>
+        <v>1327.9400000000001</v>
       </c>
       <c r="L5" s="0">
-        <v>25.489999999999998</v>
+        <v>17.489999999999998</v>
       </c>
       <c r="M5" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.056000000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -391,40 +406,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>18909375570</v>
+        <v>9858075782</v>
       </c>
       <c r="C6" s="0">
-        <v>21895248990</v>
+        <v>12305831504</v>
       </c>
       <c r="D6" s="0">
-        <v>833153</v>
+        <v>121611</v>
       </c>
       <c r="E6" s="0">
-        <v>184</v>
+        <v>68</v>
       </c>
       <c r="F6" s="0">
-        <v>107080</v>
+        <v>380324</v>
       </c>
       <c r="G6" s="0">
-        <v>4.0700000000000003</v>
+        <v>3.7599999999999998</v>
       </c>
       <c r="H6" s="0">
-        <v>11.720000000000001</v>
+        <v>6.2000000000000002</v>
       </c>
       <c r="I6" s="0">
-        <v>86.359999999999999</v>
+        <v>80.109999999999999</v>
       </c>
       <c r="J6" s="0">
-        <v>1106</v>
+        <v>474</v>
       </c>
       <c r="K6" s="0">
-        <v>3508</v>
+        <v>1327.03</v>
       </c>
       <c r="L6" s="0">
-        <v>19</v>
+        <v>19.440000000000001</v>
       </c>
       <c r="M6" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.068000000000000005</v>
       </c>
     </row>
     <row r="7">
@@ -432,40 +447,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>16300705642</v>
+        <v>6583891051</v>
       </c>
       <c r="C7" s="0">
-        <v>18977632819</v>
+        <v>8092513481</v>
       </c>
       <c r="D7" s="0">
-        <v>1014847</v>
+        <v>277141</v>
       </c>
       <c r="E7" s="0">
-        <v>165</v>
+        <v>100</v>
       </c>
       <c r="F7" s="0">
-        <v>85837</v>
+        <v>151171</v>
       </c>
       <c r="G7" s="0">
-        <v>4.5899999999999999</v>
+        <v>5.1799999999999997</v>
       </c>
       <c r="H7" s="0">
-        <v>9.9199999999999999</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="I7" s="0">
-        <v>85.890000000000001</v>
+        <v>81.359999999999999</v>
       </c>
       <c r="J7" s="0">
-        <v>849</v>
+        <v>536</v>
       </c>
       <c r="K7" s="0">
-        <v>6129</v>
+        <v>3004.3400000000001</v>
       </c>
       <c r="L7" s="0">
-        <v>25.530000000000001</v>
+        <v>30.109999999999999</v>
       </c>
       <c r="M7" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.10100000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -473,40 +488,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>47244768437</v>
+        <v>13884729196</v>
       </c>
       <c r="C8" s="0">
-        <v>56034016620</v>
+        <v>17602965883</v>
       </c>
       <c r="D8" s="0">
-        <v>657291</v>
+        <v>208418</v>
       </c>
       <c r="E8" s="0">
-        <v>138</v>
+        <v>76</v>
       </c>
       <c r="F8" s="0">
-        <v>354379</v>
+        <v>453275</v>
       </c>
       <c r="G8" s="0">
-        <v>4.1600000000000001</v>
+        <v>5.3700000000000001</v>
       </c>
       <c r="H8" s="0">
-        <v>11.74</v>
+        <v>9.4100000000000001</v>
       </c>
       <c r="I8" s="0">
-        <v>84.310000000000002</v>
+        <v>78.879999999999995</v>
       </c>
       <c r="J8" s="0">
-        <v>1070</v>
+        <v>509</v>
       </c>
       <c r="K8" s="0">
-        <v>3377</v>
+        <v>1096.5599999999999</v>
       </c>
       <c r="L8" s="0">
-        <v>23.239999999999998</v>
+        <v>14.359999999999999</v>
       </c>
       <c r="M8" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.049000000000000002</v>
       </c>
     </row>
     <row r="9">
@@ -514,40 +529,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>122610040911</v>
+        <v>43286549144</v>
       </c>
       <c r="C9" s="0">
-        <v>145841405681</v>
+        <v>51801019151</v>
       </c>
       <c r="D9" s="0">
-        <v>605679</v>
+        <v>450522</v>
       </c>
       <c r="E9" s="0">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="F9" s="0">
-        <v>1249776</v>
+        <v>439609</v>
       </c>
       <c r="G9" s="0">
-        <v>5.1900000000000004</v>
+        <v>3.8199999999999998</v>
       </c>
       <c r="H9" s="0">
-        <v>10.779999999999999</v>
+        <v>9.2799999999999994</v>
       </c>
       <c r="I9" s="0">
-        <v>84.069999999999993</v>
+        <v>83.560000000000002</v>
       </c>
       <c r="J9" s="0">
-        <v>769</v>
+        <v>877</v>
       </c>
       <c r="K9" s="0">
-        <v>3423</v>
+        <v>3438.4299999999998</v>
       </c>
       <c r="L9" s="0">
-        <v>22.640000000000001</v>
+        <v>25.649999999999999</v>
       </c>
       <c r="M9" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.070999999999999994</v>
       </c>
     </row>
     <row r="10">
@@ -555,40 +570,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>24603408621</v>
+        <v>87690276804</v>
       </c>
       <c r="C10" s="0">
-        <v>29584832718</v>
+        <v>103765339506</v>
       </c>
       <c r="D10" s="0">
-        <v>781221</v>
+        <v>641398</v>
       </c>
       <c r="E10" s="0">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="F10" s="0">
-        <v>164228</v>
+        <v>627880</v>
       </c>
       <c r="G10" s="0">
-        <v>4.3399999999999999</v>
+        <v>3.8799999999999999</v>
       </c>
       <c r="H10" s="0">
-        <v>11.48</v>
+        <v>10.640000000000001</v>
       </c>
       <c r="I10" s="0">
-        <v>83.159999999999997</v>
+        <v>84.510000000000005</v>
       </c>
       <c r="J10" s="0">
-        <v>1006</v>
+        <v>1041</v>
       </c>
       <c r="K10" s="0">
-        <v>3155</v>
+        <v>3654.6999999999998</v>
       </c>
       <c r="L10" s="0">
-        <v>17.620000000000001</v>
+        <v>23.030000000000001</v>
       </c>
       <c r="M10" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.060999999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -596,40 +611,40 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>3924750677</v>
+        <v>79618653594</v>
       </c>
       <c r="C11" s="0">
-        <v>4984255910</v>
+        <v>93178764191</v>
       </c>
       <c r="D11" s="0">
-        <v>577550</v>
+        <v>813646</v>
       </c>
       <c r="E11" s="0">
-        <v>155</v>
+        <v>189</v>
       </c>
       <c r="F11" s="0">
-        <v>24709</v>
+        <v>400498</v>
       </c>
       <c r="G11" s="0">
-        <v>2.8599999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="H11" s="0">
-        <v>9.1799999999999997</v>
+        <v>11.31</v>
       </c>
       <c r="I11" s="0">
-        <v>78.739999999999995</v>
+        <v>85.450000000000003</v>
       </c>
       <c r="J11" s="0">
-        <v>1294</v>
+        <v>1261</v>
       </c>
       <c r="K11" s="0">
-        <v>3817</v>
+        <v>4097.6099999999997</v>
       </c>
       <c r="L11" s="0">
-        <v>24.510000000000002</v>
+        <v>22.129999999999999</v>
       </c>
       <c r="M11" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.057000000000000002</v>
       </c>
     </row>
     <row r="12">
@@ -637,40 +652,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>186625137750</v>
+        <v>9447223831</v>
       </c>
       <c r="C12" s="0">
-        <v>225556684607</v>
+        <v>11364192983</v>
       </c>
       <c r="D12" s="0">
-        <v>65535</v>
+        <v>284318</v>
       </c>
       <c r="E12" s="0">
-        <v>171</v>
+        <v>115</v>
       </c>
       <c r="F12" s="0">
-        <v>745072</v>
+        <v>225245</v>
       </c>
       <c r="G12" s="0">
-        <v>65535</v>
+        <v>5.6399999999999997</v>
       </c>
       <c r="H12" s="0">
-        <v>65535</v>
+        <v>8.5099999999999998</v>
       </c>
       <c r="I12" s="0">
-        <v>82.739999999999995</v>
+        <v>83.129999999999995</v>
       </c>
       <c r="J12" s="0">
-        <v>1570</v>
+        <v>452</v>
       </c>
       <c r="K12" s="0">
-        <v>4947</v>
+        <v>3759.0700000000002</v>
       </c>
       <c r="L12" s="0">
-        <v>26.329999999999998</v>
+        <v>33.409999999999997</v>
       </c>
       <c r="M12" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="13">
@@ -678,40 +693,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>353592499</v>
+        <v>91161376592</v>
       </c>
       <c r="C13" s="0">
-        <v>423420800</v>
+        <v>109381505540</v>
       </c>
       <c r="D13" s="0">
-        <v>65535</v>
+        <v>531468</v>
       </c>
       <c r="E13" s="0">
-        <v>50</v>
+        <v>141</v>
       </c>
       <c r="F13" s="0">
-        <v>22337</v>
+        <v>1076832</v>
       </c>
       <c r="G13" s="0">
-        <v>65535</v>
+        <v>5.2300000000000004</v>
       </c>
       <c r="H13" s="0">
-        <v>65535</v>
+        <v>10.42</v>
       </c>
       <c r="I13" s="0">
-        <v>83.510000000000005</v>
+        <v>83.340000000000003</v>
       </c>
       <c r="J13" s="0">
-        <v>379</v>
+        <v>721</v>
       </c>
       <c r="K13" s="0">
-        <v>0</v>
+        <v>3592.1900000000001</v>
       </c>
       <c r="L13" s="0">
-        <v>0</v>
+        <v>25.489999999999998</v>
       </c>
       <c r="M13" s="0">
-        <v>0</v>
+        <v>0.070000000000000007</v>
       </c>
     </row>
     <row r="14">
@@ -719,40 +734,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>5815895253</v>
+        <v>153937603405</v>
       </c>
       <c r="C14" s="0">
-        <v>7343427295</v>
+        <v>181548105057</v>
       </c>
       <c r="D14" s="0">
-        <v>146167</v>
+        <v>664476</v>
       </c>
       <c r="E14" s="0">
-        <v>65</v>
+        <v>165</v>
       </c>
       <c r="F14" s="0">
-        <v>232822</v>
+        <v>962368</v>
       </c>
       <c r="G14" s="0">
-        <v>4.6299999999999999</v>
+        <v>3.52</v>
       </c>
       <c r="H14" s="0">
-        <v>7.9000000000000004</v>
+        <v>10.380000000000001</v>
       </c>
       <c r="I14" s="0">
-        <v>79.200000000000003</v>
+        <v>84.790000000000006</v>
       </c>
       <c r="J14" s="0">
-        <v>464</v>
+        <v>1147</v>
       </c>
       <c r="K14" s="0">
-        <v>1101</v>
+        <v>3704.4499999999998</v>
       </c>
       <c r="L14" s="0">
-        <v>16.489999999999998</v>
+        <v>22.530000000000001</v>
       </c>
       <c r="M14" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.058000000000000003</v>
       </c>
     </row>
     <row r="15">
@@ -760,40 +775,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>5771366742</v>
+        <v>38900540444</v>
       </c>
       <c r="C15" s="0">
-        <v>7489840226</v>
+        <v>45040396519</v>
       </c>
       <c r="D15" s="0">
-        <v>46602</v>
+        <v>771108</v>
       </c>
       <c r="E15" s="0">
-        <v>60</v>
+        <v>179</v>
       </c>
       <c r="F15" s="0">
-        <v>253834</v>
+        <v>204022</v>
       </c>
       <c r="G15" s="0">
-        <v>1.5800000000000001</v>
+        <v>3.4900000000000002</v>
       </c>
       <c r="H15" s="0">
-        <v>2.6600000000000001</v>
+        <v>10.91</v>
       </c>
       <c r="I15" s="0">
-        <v>77.060000000000002</v>
+        <v>86.370000000000005</v>
       </c>
       <c r="J15" s="0">
-        <v>478</v>
+        <v>1235</v>
       </c>
       <c r="K15" s="0">
-        <v>1473</v>
+        <v>3535.4699999999998</v>
       </c>
       <c r="L15" s="0">
-        <v>24.260000000000002</v>
+        <v>19.780000000000001</v>
       </c>
       <c r="M15" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.050000000000000003</v>
       </c>
     </row>
     <row r="16">
@@ -801,40 +816,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>2716702713</v>
+        <v>36360150286</v>
       </c>
       <c r="C16" s="0">
-        <v>3347378746</v>
+        <v>41662915500</v>
       </c>
       <c r="D16" s="0">
-        <v>169918</v>
+        <v>825172</v>
       </c>
       <c r="E16" s="0">
-        <v>71</v>
+        <v>180</v>
       </c>
       <c r="F16" s="0">
-        <v>95288</v>
+        <v>179953</v>
       </c>
       <c r="G16" s="0">
-        <v>4.8399999999999999</v>
+        <v>3.5600000000000001</v>
       </c>
       <c r="H16" s="0">
-        <v>8.1400000000000006</v>
+        <v>11.449999999999999</v>
       </c>
       <c r="I16" s="0">
-        <v>81.159999999999997</v>
+        <v>87.269999999999996</v>
       </c>
       <c r="J16" s="0">
-        <v>495</v>
+        <v>1289</v>
       </c>
       <c r="K16" s="0">
-        <v>1140</v>
+        <v>3508.29</v>
       </c>
       <c r="L16" s="0">
-        <v>16.07</v>
+        <v>19.530000000000001</v>
       </c>
       <c r="M16" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.049000000000000002</v>
       </c>
     </row>
     <row r="17">
@@ -842,40 +857,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>365226560</v>
+        <v>49455164252</v>
       </c>
       <c r="C17" s="0">
-        <v>456905692</v>
+        <v>57527592939</v>
       </c>
       <c r="D17" s="0">
-        <v>229601</v>
+        <v>774261</v>
       </c>
       <c r="E17" s="0">
-        <v>76</v>
+        <v>180</v>
       </c>
       <c r="F17" s="0">
-        <v>7137</v>
+        <v>182494</v>
       </c>
       <c r="G17" s="0">
-        <v>3.5899999999999999</v>
+        <v>2.46</v>
       </c>
       <c r="H17" s="0">
-        <v>8.4499999999999993</v>
+        <v>10.26</v>
       </c>
       <c r="I17" s="0">
-        <v>79.930000000000007</v>
+        <v>85.969999999999999</v>
       </c>
       <c r="J17" s="0">
-        <v>842</v>
+        <v>1770</v>
       </c>
       <c r="K17" s="0">
-        <v>747</v>
+        <v>4666.8900000000003</v>
       </c>
       <c r="L17" s="0">
-        <v>9.8300000000000001</v>
+        <v>26.18</v>
       </c>
       <c r="M17" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.062</v>
       </c>
     </row>
     <row r="18">
@@ -883,40 +898,40 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>7534935992</v>
+        <v>11098385803</v>
       </c>
       <c r="C18" s="0">
-        <v>9338287750</v>
+        <v>12545747746</v>
       </c>
       <c r="D18" s="0">
-        <v>220035</v>
+        <v>0</v>
       </c>
       <c r="E18" s="0">
-        <v>76</v>
+        <v>223</v>
       </c>
       <c r="F18" s="0">
-        <v>222137</v>
+        <v>36005</v>
       </c>
       <c r="G18" s="0">
-        <v>5.2300000000000004</v>
+        <v>0</v>
       </c>
       <c r="H18" s="0">
-        <v>9.2300000000000004</v>
+        <v>0</v>
       </c>
       <c r="I18" s="0">
-        <v>80.689999999999998</v>
+        <v>88.459999999999994</v>
       </c>
       <c r="J18" s="0">
-        <v>553</v>
+        <v>1563</v>
       </c>
       <c r="K18" s="0">
-        <v>1050</v>
+        <v>4757.8400000000001</v>
       </c>
       <c r="L18" s="0">
-        <v>13.82</v>
+        <v>21.350000000000001</v>
       </c>
       <c r="M18" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.050999999999999997</v>
       </c>
     </row>
     <row r="19">
@@ -924,40 +939,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>502878086</v>
+        <v>42078717441</v>
       </c>
       <c r="C19" s="0">
-        <v>652355850</v>
+        <v>51645275069</v>
       </c>
       <c r="D19" s="0">
-        <v>65535</v>
+        <v>0</v>
       </c>
       <c r="E19" s="0">
-        <v>50</v>
+        <v>215</v>
       </c>
       <c r="F19" s="0">
-        <v>41120</v>
+        <v>72968</v>
       </c>
       <c r="G19" s="0">
-        <v>65535</v>
+        <v>0</v>
       </c>
       <c r="H19" s="0">
-        <v>65535</v>
+        <v>0</v>
       </c>
       <c r="I19" s="0">
-        <v>77.090000000000003</v>
+        <v>81.480000000000004</v>
       </c>
       <c r="J19" s="0">
-        <v>317</v>
+        <v>3321</v>
       </c>
       <c r="K19" s="0">
-        <v>0</v>
+        <v>6186.2600000000002</v>
       </c>
       <c r="L19" s="0">
-        <v>0</v>
+        <v>29.010000000000002</v>
       </c>
       <c r="M19" s="0">
-        <v>0</v>
+        <v>0.062</v>
       </c>
     </row>
     <row r="20">
@@ -965,40 +980,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>4931410143</v>
+        <v>15789309805</v>
       </c>
       <c r="C20" s="0">
-        <v>6375728160</v>
+        <v>19340224456</v>
       </c>
       <c r="D20" s="0">
-        <v>146737</v>
+        <v>1441149</v>
       </c>
       <c r="E20" s="0">
-        <v>67</v>
+        <v>244</v>
       </c>
       <c r="F20" s="0">
-        <v>245263</v>
+        <v>20747</v>
       </c>
       <c r="G20" s="0">
-        <v>5.6399999999999997</v>
+        <v>1.55</v>
       </c>
       <c r="H20" s="0">
-        <v>8.5</v>
+        <v>12.390000000000001</v>
       </c>
       <c r="I20" s="0">
-        <v>77.349999999999994</v>
+        <v>81.640000000000001</v>
       </c>
       <c r="J20" s="0">
-        <v>389</v>
+        <v>3827</v>
       </c>
       <c r="K20" s="0">
-        <v>1316</v>
+        <v>6269.6899999999996</v>
       </c>
       <c r="L20" s="0">
-        <v>19.699999999999999</v>
+        <v>25.739999999999998</v>
       </c>
       <c r="M20" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.053999999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -1006,40 +1021,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>10044134336</v>
+        <v>23361124561</v>
       </c>
       <c r="C21" s="0">
-        <v>13215784917</v>
+        <v>28078529663</v>
       </c>
       <c r="D21" s="0">
-        <v>204294</v>
+        <v>1564263</v>
       </c>
       <c r="E21" s="0">
-        <v>74</v>
+        <v>267</v>
       </c>
       <c r="F21" s="0">
-        <v>304071</v>
+        <v>30774</v>
       </c>
       <c r="G21" s="0">
-        <v>4.7000000000000002</v>
+        <v>1.71</v>
       </c>
       <c r="H21" s="0">
-        <v>9.2899999999999991</v>
+        <v>12.630000000000001</v>
       </c>
       <c r="I21" s="0">
-        <v>76</v>
+        <v>83.200000000000003</v>
       </c>
       <c r="J21" s="0">
-        <v>587</v>
+        <v>3467</v>
       </c>
       <c r="K21" s="0">
-        <v>1331</v>
+        <v>7077.04</v>
       </c>
       <c r="L21" s="0">
-        <v>17.969999999999999</v>
+        <v>26.850000000000001</v>
       </c>
       <c r="M21" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.057000000000000002</v>
       </c>
     </row>
     <row r="22">
@@ -1047,40 +1062,40 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>18830034665</v>
+        <v>22820707926</v>
       </c>
       <c r="C22" s="0">
-        <v>23236115188</v>
+        <v>26713192336</v>
       </c>
       <c r="D22" s="0">
-        <v>162434</v>
+        <v>1856372</v>
       </c>
       <c r="E22" s="0">
-        <v>62</v>
+        <v>291</v>
       </c>
       <c r="F22" s="0">
-        <v>732281</v>
+        <v>23099</v>
       </c>
       <c r="G22" s="0">
-        <v>5.1200000000000001</v>
+        <v>1.6100000000000001</v>
       </c>
       <c r="H22" s="0">
-        <v>8.6999999999999993</v>
+        <v>13.289999999999999</v>
       </c>
       <c r="I22" s="0">
-        <v>81.040000000000006</v>
+        <v>85.430000000000007</v>
       </c>
       <c r="J22" s="0">
-        <v>483</v>
+        <v>3968</v>
       </c>
       <c r="K22" s="0">
-        <v>1361</v>
+        <v>6957.0799999999999</v>
       </c>
       <c r="L22" s="0">
-        <v>21.149999999999999</v>
+        <v>23.870000000000001</v>
       </c>
       <c r="M22" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.050000000000000003</v>
       </c>
     </row>
     <row r="23">
@@ -1088,40 +1103,245 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
+        <v>299725643</v>
+      </c>
+      <c r="C23" s="0">
+        <v>329828276</v>
+      </c>
+      <c r="D23" s="0">
+        <v>845714</v>
+      </c>
+      <c r="E23" s="0">
+        <v>306</v>
+      </c>
+      <c r="F23" s="0">
+        <v>168</v>
+      </c>
+      <c r="G23" s="0">
+        <v>0.42999999999999999</v>
+      </c>
+      <c r="H23" s="0">
+        <v>5.46</v>
+      </c>
+      <c r="I23" s="0">
+        <v>90.870000000000005</v>
+      </c>
+      <c r="J23" s="0">
+        <v>6423</v>
+      </c>
+      <c r="K23" s="0">
+        <v>7624.1800000000003</v>
+      </c>
+      <c r="L23" s="0">
+        <v>24.940000000000001</v>
+      </c>
+      <c r="M23" s="0">
+        <v>0.049000000000000002</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="0">
+        <v>13341449274</v>
+      </c>
+      <c r="C24" s="0">
+        <v>16605195881</v>
+      </c>
+      <c r="D24" s="0">
+        <v>1442676</v>
+      </c>
+      <c r="E24" s="0">
+        <v>223</v>
+      </c>
+      <c r="F24" s="0">
+        <v>14888</v>
+      </c>
+      <c r="G24" s="0">
+        <v>1.29</v>
+      </c>
+      <c r="H24" s="0">
+        <v>12.890000000000001</v>
+      </c>
+      <c r="I24" s="0">
+        <v>80.349999999999994</v>
+      </c>
+      <c r="J24" s="0">
+        <v>5004</v>
+      </c>
+      <c r="K24" s="0">
+        <v>7234.9700000000003</v>
+      </c>
+      <c r="L24" s="0">
+        <v>32.460000000000001</v>
+      </c>
+      <c r="M24" s="0">
+        <v>0.065000000000000002</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="0">
+        <v>15262415406</v>
+      </c>
+      <c r="C25" s="0">
+        <v>19194311381</v>
+      </c>
+      <c r="D25" s="0">
+        <v>1788845</v>
+      </c>
+      <c r="E25" s="0">
+        <v>262</v>
+      </c>
+      <c r="F25" s="0">
+        <v>12837</v>
+      </c>
+      <c r="G25" s="0">
+        <v>1.2</v>
+      </c>
+      <c r="H25" s="0">
+        <v>13.35</v>
+      </c>
+      <c r="I25" s="0">
+        <v>79.519999999999996</v>
+      </c>
+      <c r="J25" s="0">
+        <v>5732</v>
+      </c>
+      <c r="K25" s="0">
+        <v>7371.5699999999997</v>
+      </c>
+      <c r="L25" s="0">
+        <v>28.25</v>
+      </c>
+      <c r="M25" s="0">
+        <v>0.055</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="0">
+        <v>68915028524</v>
+      </c>
+      <c r="C26" s="0">
+        <v>84766010508</v>
+      </c>
+      <c r="D26" s="0">
+        <v>1672903</v>
+      </c>
+      <c r="E26" s="0">
+        <v>290</v>
+      </c>
+      <c r="F26" s="0">
+        <v>66934</v>
+      </c>
+      <c r="G26" s="0">
+        <v>1.3200000000000001</v>
+      </c>
+      <c r="H26" s="0">
+        <v>11.93</v>
+      </c>
+      <c r="I26" s="0">
+        <v>81.299999999999997</v>
+      </c>
+      <c r="J26" s="0">
+        <v>4476</v>
+      </c>
+      <c r="K26" s="0">
+        <v>8755.1900000000005</v>
+      </c>
+      <c r="L26" s="0">
+        <v>30.890000000000001</v>
+      </c>
+      <c r="M26" s="0">
+        <v>0.062</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="0">
+        <v>16472096294</v>
+      </c>
+      <c r="C27" s="0">
+        <v>20885405745</v>
+      </c>
+      <c r="D27" s="0">
+        <v>1864768</v>
+      </c>
+      <c r="E27" s="0">
+        <v>325</v>
+      </c>
+      <c r="F27" s="0">
+        <v>12753</v>
+      </c>
+      <c r="G27" s="0">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="H27" s="0">
+        <v>11.48</v>
+      </c>
+      <c r="I27" s="0">
+        <v>78.870000000000005</v>
+      </c>
+      <c r="J27" s="0">
+        <v>5037</v>
+      </c>
+      <c r="K27" s="0">
+        <v>10262.379999999999</v>
+      </c>
+      <c r="L27" s="0">
+        <v>31.579999999999998</v>
+      </c>
+      <c r="M27" s="0">
+        <v>0.063</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="0">
         <v>882746567069</v>
       </c>
-      <c r="C23" s="0">
+      <c r="C28" s="0">
         <v>1055345310552</v>
       </c>
-      <c r="D23" s="0">
-        <v>65535</v>
-      </c>
-      <c r="E23" s="0">
+      <c r="D28" s="0">
+        <v>0</v>
+      </c>
+      <c r="E28" s="0">
         <v>131</v>
       </c>
-      <c r="F23" s="0">
+      <c r="F28" s="0">
         <v>6897535</v>
       </c>
-      <c r="G23" s="0">
-        <v>65535</v>
-      </c>
-      <c r="H23" s="0">
-        <v>65535</v>
-      </c>
-      <c r="I23" s="0">
+      <c r="G28" s="0">
+        <v>0</v>
+      </c>
+      <c r="H28" s="0">
+        <v>0</v>
+      </c>
+      <c r="I28" s="0">
         <v>83.650000000000006</v>
       </c>
-      <c r="J23" s="0">
+      <c r="J28" s="0">
         <v>951</v>
       </c>
-      <c r="K23" s="0">
-        <v>3680</v>
-      </c>
-      <c r="L23" s="0">
+      <c r="K28" s="0">
+        <v>3680.21</v>
+      </c>
+      <c r="L28" s="0">
         <v>24.260000000000002</v>
       </c>
-      <c r="M23" s="0">
-        <v>0.059999999999999998</v>
+      <c r="M28" s="0">
+        <v>0.060999999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2017/Aircraft_Cumulative_Statistics_2017.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2017/Aircraft_Cumulative_Statistics_2017.xlsx
@@ -13,11 +13,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="49" uniqueCount="49">
   <si>
     <t>Row</t>
   </si>
   <si>
+    <t>E140</t>
+  </si>
+  <si>
     <t>E145</t>
   </si>
   <si>
@@ -30,6 +33,18 @@
     <t>E175</t>
   </si>
   <si>
+    <t>Q100</t>
+  </si>
+  <si>
+    <t>Q200</t>
+  </si>
+  <si>
+    <t>Q300</t>
+  </si>
+  <si>
+    <t>Q400</t>
+  </si>
+  <si>
     <t>CRJ-700</t>
   </si>
   <si>
@@ -48,7 +63,19 @@
     <t>A321</t>
   </si>
   <si>
+    <t>MD-80</t>
+  </si>
+  <si>
+    <t>MD-90</t>
+  </si>
+  <si>
     <t>B717-200</t>
+  </si>
+  <si>
+    <t>B737-300</t>
+  </si>
+  <si>
+    <t>B737-400</t>
   </si>
   <si>
     <t>B737-700</t>
@@ -178,7 +205,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="true"/>
@@ -201,40 +228,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2">
@@ -242,40 +269,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>2890747483</v>
+        <v>78475440</v>
       </c>
       <c r="C2" s="0">
-        <v>3765248500</v>
+        <v>106658552</v>
       </c>
       <c r="D2" s="0">
-        <v>48026</v>
+        <v>27071</v>
       </c>
       <c r="E2" s="0">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F2" s="0">
-        <v>199282</v>
+        <v>8437</v>
       </c>
       <c r="G2" s="0">
-        <v>2.54</v>
+        <v>2.1400000000000001</v>
       </c>
       <c r="H2" s="0">
-        <v>3.8599999999999999</v>
+        <v>2.6499999999999999</v>
       </c>
       <c r="I2" s="0">
-        <v>76.769999999999996</v>
+        <v>73.579999999999998</v>
       </c>
       <c r="J2" s="0">
-        <v>378</v>
+        <v>287</v>
       </c>
       <c r="K2" s="0">
-        <v>1013.04</v>
+        <v>1477.1800000000001</v>
       </c>
       <c r="L2" s="0">
-        <v>20.260000000000002</v>
+        <v>33.57</v>
       </c>
       <c r="M2" s="0">
-        <v>0.082000000000000003</v>
+        <v>0.14399999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -283,40 +310,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>6922199171</v>
+        <v>2890747483</v>
       </c>
       <c r="C3" s="0">
-        <v>8832929270</v>
+        <v>3765248500</v>
       </c>
       <c r="D3" s="0">
-        <v>91476</v>
+        <v>48026</v>
       </c>
       <c r="E3" s="0">
         <v>50</v>
       </c>
       <c r="F3" s="0">
-        <v>512122</v>
+        <v>199282</v>
       </c>
       <c r="G3" s="0">
-        <v>5.2999999999999998</v>
+        <v>2.54</v>
       </c>
       <c r="H3" s="0">
-        <v>7.5099999999999998</v>
+        <v>3.8599999999999999</v>
       </c>
       <c r="I3" s="0">
-        <v>78.370000000000005</v>
+        <v>76.769999999999996</v>
       </c>
       <c r="J3" s="0">
-        <v>345</v>
+        <v>378</v>
       </c>
       <c r="K3" s="0">
-        <v>1343.8800000000001</v>
+        <v>1013.04</v>
       </c>
       <c r="L3" s="0">
-        <v>26.879999999999999</v>
+        <v>20.260000000000002</v>
       </c>
       <c r="M3" s="0">
-        <v>0.11</v>
+        <v>0.082000000000000003</v>
       </c>
     </row>
     <row r="4">
@@ -324,40 +351,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>3116338885</v>
+        <v>6922199171</v>
       </c>
       <c r="C4" s="0">
-        <v>3972814249</v>
+        <v>8832929270</v>
       </c>
       <c r="D4" s="0">
-        <v>145738</v>
+        <v>91476</v>
       </c>
       <c r="E4" s="0">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F4" s="0">
-        <v>90996</v>
+        <v>512122</v>
       </c>
       <c r="G4" s="0">
-        <v>3.3399999999999999</v>
+        <v>5.2999999999999998</v>
       </c>
       <c r="H4" s="0">
-        <v>6.8099999999999996</v>
+        <v>7.5099999999999998</v>
       </c>
       <c r="I4" s="0">
-        <v>78.439999999999998</v>
+        <v>78.370000000000005</v>
       </c>
       <c r="J4" s="0">
-        <v>626</v>
+        <v>345</v>
       </c>
       <c r="K4" s="0">
-        <v>1351.4400000000001</v>
+        <v>1343.8800000000001</v>
       </c>
       <c r="L4" s="0">
-        <v>19.399999999999999</v>
+        <v>26.879999999999999</v>
       </c>
       <c r="M4" s="0">
-        <v>0.063</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="5">
@@ -365,40 +392,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>20194086472</v>
+        <v>3116338885</v>
       </c>
       <c r="C5" s="0">
-        <v>25399455218</v>
+        <v>3972814249</v>
       </c>
       <c r="D5" s="0">
-        <v>183509</v>
+        <v>145738</v>
       </c>
       <c r="E5" s="0">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F5" s="0">
-        <v>520291</v>
+        <v>90996</v>
       </c>
       <c r="G5" s="0">
-        <v>3.7599999999999998</v>
+        <v>3.3399999999999999</v>
       </c>
       <c r="H5" s="0">
-        <v>7.71</v>
+        <v>6.8099999999999996</v>
       </c>
       <c r="I5" s="0">
-        <v>79.510000000000005</v>
+        <v>78.439999999999998</v>
       </c>
       <c r="J5" s="0">
-        <v>643</v>
+        <v>626</v>
       </c>
       <c r="K5" s="0">
-        <v>1327.9400000000001</v>
+        <v>1351.4400000000001</v>
       </c>
       <c r="L5" s="0">
-        <v>17.489999999999998</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="M5" s="0">
-        <v>0.056000000000000001</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="6">
@@ -406,40 +433,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>9858075782</v>
+        <v>20194086472</v>
       </c>
       <c r="C6" s="0">
-        <v>12305831504</v>
+        <v>25399455218</v>
       </c>
       <c r="D6" s="0">
-        <v>121611</v>
+        <v>183509</v>
       </c>
       <c r="E6" s="0">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="F6" s="0">
-        <v>380324</v>
+        <v>520291</v>
       </c>
       <c r="G6" s="0">
         <v>3.7599999999999998</v>
       </c>
       <c r="H6" s="0">
-        <v>6.2000000000000002</v>
+        <v>7.71</v>
       </c>
       <c r="I6" s="0">
-        <v>80.109999999999999</v>
+        <v>79.510000000000005</v>
       </c>
       <c r="J6" s="0">
-        <v>474</v>
+        <v>643</v>
       </c>
       <c r="K6" s="0">
-        <v>1327.03</v>
+        <v>1327.9400000000001</v>
       </c>
       <c r="L6" s="0">
-        <v>19.440000000000001</v>
+        <v>17.489999999999998</v>
       </c>
       <c r="M6" s="0">
-        <v>0.068000000000000005</v>
+        <v>0.056000000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -447,40 +474,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>6583891051</v>
+        <v>81514508</v>
       </c>
       <c r="C7" s="0">
-        <v>8092513481</v>
+        <v>116049885</v>
       </c>
       <c r="D7" s="0">
-        <v>277141</v>
+        <v>0</v>
       </c>
       <c r="E7" s="0">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="F7" s="0">
-        <v>151171</v>
+        <v>18791</v>
       </c>
       <c r="G7" s="0">
-        <v>5.1799999999999997</v>
+        <v>0</v>
       </c>
       <c r="H7" s="0">
-        <v>9.3000000000000007</v>
+        <v>0</v>
       </c>
       <c r="I7" s="0">
-        <v>81.359999999999999</v>
+        <v>70.239999999999995</v>
       </c>
       <c r="J7" s="0">
-        <v>536</v>
+        <v>167</v>
       </c>
       <c r="K7" s="0">
-        <v>3004.3400000000001</v>
+        <v>0</v>
       </c>
       <c r="L7" s="0">
-        <v>30.109999999999999</v>
+        <v>0</v>
       </c>
       <c r="M7" s="0">
-        <v>0.10100000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -488,40 +515,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>13884729196</v>
+        <v>99131135</v>
       </c>
       <c r="C8" s="0">
-        <v>17602965883</v>
+        <v>130957467</v>
       </c>
       <c r="D8" s="0">
-        <v>208418</v>
+        <v>0</v>
       </c>
       <c r="E8" s="0">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="F8" s="0">
-        <v>453275</v>
+        <v>18964</v>
       </c>
       <c r="G8" s="0">
-        <v>5.3700000000000001</v>
+        <v>0</v>
       </c>
       <c r="H8" s="0">
-        <v>9.4100000000000001</v>
+        <v>0</v>
       </c>
       <c r="I8" s="0">
-        <v>78.879999999999995</v>
+        <v>75.700000000000003</v>
       </c>
       <c r="J8" s="0">
-        <v>509</v>
+        <v>187</v>
       </c>
       <c r="K8" s="0">
-        <v>1096.5599999999999</v>
+        <v>0</v>
       </c>
       <c r="L8" s="0">
-        <v>14.359999999999999</v>
+        <v>0</v>
       </c>
       <c r="M8" s="0">
-        <v>0.049000000000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -529,40 +556,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>43286549144</v>
+        <v>192910581</v>
       </c>
       <c r="C9" s="0">
-        <v>51801019151</v>
+        <v>256332699</v>
       </c>
       <c r="D9" s="0">
-        <v>450522</v>
+        <v>0</v>
       </c>
       <c r="E9" s="0">
-        <v>134</v>
+        <v>48</v>
       </c>
       <c r="F9" s="0">
-        <v>439609</v>
+        <v>31511</v>
       </c>
       <c r="G9" s="0">
-        <v>3.8199999999999998</v>
+        <v>0</v>
       </c>
       <c r="H9" s="0">
-        <v>9.2799999999999994</v>
+        <v>0</v>
       </c>
       <c r="I9" s="0">
-        <v>83.560000000000002</v>
+        <v>75.260000000000005</v>
       </c>
       <c r="J9" s="0">
-        <v>877</v>
+        <v>168</v>
       </c>
       <c r="K9" s="0">
-        <v>3438.4299999999998</v>
+        <v>0</v>
       </c>
       <c r="L9" s="0">
-        <v>25.649999999999999</v>
+        <v>0</v>
       </c>
       <c r="M9" s="0">
-        <v>0.070999999999999994</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -570,40 +597,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>87690276804</v>
+        <v>1978246870</v>
       </c>
       <c r="C10" s="0">
-        <v>103765339506</v>
+        <v>2487835908</v>
       </c>
       <c r="D10" s="0">
-        <v>641398</v>
+        <v>131981</v>
       </c>
       <c r="E10" s="0">
-        <v>159</v>
+        <v>76</v>
       </c>
       <c r="F10" s="0">
-        <v>627880</v>
+        <v>111320</v>
       </c>
       <c r="G10" s="0">
-        <v>3.8799999999999999</v>
+        <v>5.9100000000000001</v>
       </c>
       <c r="H10" s="0">
-        <v>10.640000000000001</v>
+        <v>7.29</v>
       </c>
       <c r="I10" s="0">
-        <v>84.510000000000005</v>
+        <v>79.519999999999996</v>
       </c>
       <c r="J10" s="0">
-        <v>1041</v>
+        <v>294</v>
       </c>
       <c r="K10" s="0">
-        <v>3654.6999999999998</v>
+        <v>1793.3</v>
       </c>
       <c r="L10" s="0">
-        <v>23.030000000000001</v>
+        <v>23.600000000000001</v>
       </c>
       <c r="M10" s="0">
-        <v>0.060999999999999999</v>
+        <v>0.099000000000000005</v>
       </c>
     </row>
     <row r="11">
@@ -611,40 +638,40 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>79618653594</v>
+        <v>9858075782</v>
       </c>
       <c r="C11" s="0">
-        <v>93178764191</v>
+        <v>12305831504</v>
       </c>
       <c r="D11" s="0">
-        <v>813646</v>
+        <v>121611</v>
       </c>
       <c r="E11" s="0">
-        <v>189</v>
+        <v>68</v>
       </c>
       <c r="F11" s="0">
-        <v>400498</v>
+        <v>380324</v>
       </c>
       <c r="G11" s="0">
-        <v>3.5</v>
+        <v>3.7599999999999998</v>
       </c>
       <c r="H11" s="0">
-        <v>11.31</v>
+        <v>6.2000000000000002</v>
       </c>
       <c r="I11" s="0">
-        <v>85.450000000000003</v>
+        <v>80.109999999999999</v>
       </c>
       <c r="J11" s="0">
-        <v>1261</v>
+        <v>474</v>
       </c>
       <c r="K11" s="0">
-        <v>4097.6099999999997</v>
+        <v>1327.03</v>
       </c>
       <c r="L11" s="0">
-        <v>22.129999999999999</v>
+        <v>19.440000000000001</v>
       </c>
       <c r="M11" s="0">
-        <v>0.057000000000000002</v>
+        <v>0.068000000000000005</v>
       </c>
     </row>
     <row r="12">
@@ -652,40 +679,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>9447223831</v>
+        <v>6583891051</v>
       </c>
       <c r="C12" s="0">
-        <v>11364192983</v>
+        <v>8092513481</v>
       </c>
       <c r="D12" s="0">
-        <v>284318</v>
+        <v>277141</v>
       </c>
       <c r="E12" s="0">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="F12" s="0">
-        <v>225245</v>
+        <v>151171</v>
       </c>
       <c r="G12" s="0">
-        <v>5.6399999999999997</v>
+        <v>5.1799999999999997</v>
       </c>
       <c r="H12" s="0">
-        <v>8.5099999999999998</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="I12" s="0">
-        <v>83.129999999999995</v>
+        <v>81.359999999999999</v>
       </c>
       <c r="J12" s="0">
-        <v>452</v>
+        <v>536</v>
       </c>
       <c r="K12" s="0">
-        <v>3759.0700000000002</v>
+        <v>3004.3400000000001</v>
       </c>
       <c r="L12" s="0">
-        <v>33.409999999999997</v>
+        <v>30.109999999999999</v>
       </c>
       <c r="M12" s="0">
-        <v>0.113</v>
+        <v>0.10100000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -693,40 +720,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>91161376592</v>
+        <v>13884729196</v>
       </c>
       <c r="C13" s="0">
-        <v>109381505540</v>
+        <v>17602965883</v>
       </c>
       <c r="D13" s="0">
-        <v>531468</v>
+        <v>208418</v>
       </c>
       <c r="E13" s="0">
-        <v>141</v>
+        <v>76</v>
       </c>
       <c r="F13" s="0">
-        <v>1076832</v>
+        <v>453275</v>
       </c>
       <c r="G13" s="0">
-        <v>5.2300000000000004</v>
+        <v>5.3700000000000001</v>
       </c>
       <c r="H13" s="0">
-        <v>10.42</v>
+        <v>9.4100000000000001</v>
       </c>
       <c r="I13" s="0">
-        <v>83.340000000000003</v>
+        <v>78.879999999999995</v>
       </c>
       <c r="J13" s="0">
-        <v>721</v>
+        <v>509</v>
       </c>
       <c r="K13" s="0">
-        <v>3592.1900000000001</v>
+        <v>1096.5599999999999</v>
       </c>
       <c r="L13" s="0">
-        <v>25.489999999999998</v>
+        <v>14.359999999999999</v>
       </c>
       <c r="M13" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.049000000000000002</v>
       </c>
     </row>
     <row r="14">
@@ -734,40 +761,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>153937603405</v>
+        <v>43286549144</v>
       </c>
       <c r="C14" s="0">
-        <v>181548105057</v>
+        <v>51801019151</v>
       </c>
       <c r="D14" s="0">
-        <v>664476</v>
+        <v>450522</v>
       </c>
       <c r="E14" s="0">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="F14" s="0">
-        <v>962368</v>
+        <v>439609</v>
       </c>
       <c r="G14" s="0">
-        <v>3.52</v>
+        <v>3.8199999999999998</v>
       </c>
       <c r="H14" s="0">
-        <v>10.380000000000001</v>
+        <v>9.2799999999999994</v>
       </c>
       <c r="I14" s="0">
-        <v>84.790000000000006</v>
+        <v>83.560000000000002</v>
       </c>
       <c r="J14" s="0">
-        <v>1147</v>
+        <v>877</v>
       </c>
       <c r="K14" s="0">
-        <v>3704.4499999999998</v>
+        <v>3438.4299999999998</v>
       </c>
       <c r="L14" s="0">
-        <v>22.530000000000001</v>
+        <v>25.649999999999999</v>
       </c>
       <c r="M14" s="0">
-        <v>0.058000000000000003</v>
+        <v>0.070999999999999994</v>
       </c>
     </row>
     <row r="15">
@@ -775,40 +802,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>38900540444</v>
+        <v>87690276804</v>
       </c>
       <c r="C15" s="0">
-        <v>45040396519</v>
+        <v>103765339506</v>
       </c>
       <c r="D15" s="0">
-        <v>771108</v>
+        <v>641398</v>
       </c>
       <c r="E15" s="0">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="F15" s="0">
-        <v>204022</v>
+        <v>627880</v>
       </c>
       <c r="G15" s="0">
-        <v>3.4900000000000002</v>
+        <v>3.8799999999999999</v>
       </c>
       <c r="H15" s="0">
-        <v>10.91</v>
+        <v>10.640000000000001</v>
       </c>
       <c r="I15" s="0">
-        <v>86.370000000000005</v>
+        <v>84.510000000000005</v>
       </c>
       <c r="J15" s="0">
-        <v>1235</v>
+        <v>1041</v>
       </c>
       <c r="K15" s="0">
-        <v>3535.4699999999998</v>
+        <v>3654.6999999999998</v>
       </c>
       <c r="L15" s="0">
-        <v>19.780000000000001</v>
+        <v>23.030000000000001</v>
       </c>
       <c r="M15" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.060999999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -816,40 +843,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>36360150286</v>
+        <v>79618653594</v>
       </c>
       <c r="C16" s="0">
-        <v>41662915500</v>
+        <v>93178764191</v>
       </c>
       <c r="D16" s="0">
-        <v>825172</v>
+        <v>813646</v>
       </c>
       <c r="E16" s="0">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="F16" s="0">
-        <v>179953</v>
+        <v>400498</v>
       </c>
       <c r="G16" s="0">
-        <v>3.5600000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="H16" s="0">
-        <v>11.449999999999999</v>
+        <v>11.31</v>
       </c>
       <c r="I16" s="0">
-        <v>87.269999999999996</v>
+        <v>85.450000000000003</v>
       </c>
       <c r="J16" s="0">
-        <v>1289</v>
+        <v>1261</v>
       </c>
       <c r="K16" s="0">
-        <v>3508.29</v>
+        <v>4097.6099999999997</v>
       </c>
       <c r="L16" s="0">
-        <v>19.530000000000001</v>
+        <v>22.129999999999999</v>
       </c>
       <c r="M16" s="0">
-        <v>0.049000000000000002</v>
+        <v>0.057000000000000002</v>
       </c>
     </row>
     <row r="17">
@@ -857,40 +884,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>49455164252</v>
+        <v>23491133023</v>
       </c>
       <c r="C17" s="0">
-        <v>57527592939</v>
+        <v>28089924872</v>
       </c>
       <c r="D17" s="0">
-        <v>774261</v>
+        <v>372397</v>
       </c>
       <c r="E17" s="0">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="F17" s="0">
-        <v>182494</v>
+        <v>317766</v>
       </c>
       <c r="G17" s="0">
-        <v>2.46</v>
+        <v>4.21</v>
       </c>
       <c r="H17" s="0">
-        <v>10.26</v>
+        <v>7.6799999999999997</v>
       </c>
       <c r="I17" s="0">
-        <v>85.969999999999999</v>
+        <v>83.629999999999995</v>
       </c>
       <c r="J17" s="0">
-        <v>1770</v>
+        <v>592</v>
       </c>
       <c r="K17" s="0">
-        <v>4666.8900000000003</v>
+        <v>4027.3000000000002</v>
       </c>
       <c r="L17" s="0">
-        <v>26.18</v>
+        <v>27.030000000000001</v>
       </c>
       <c r="M17" s="0">
-        <v>0.062</v>
+        <v>0.083000000000000004</v>
       </c>
     </row>
     <row r="18">
@@ -898,40 +925,40 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>11098385803</v>
+        <v>9464085199</v>
       </c>
       <c r="C18" s="0">
-        <v>12545747746</v>
+        <v>11025047014</v>
       </c>
       <c r="D18" s="0">
-        <v>0</v>
+        <v>471156</v>
       </c>
       <c r="E18" s="0">
-        <v>223</v>
+        <v>159</v>
       </c>
       <c r="F18" s="0">
-        <v>36005</v>
+        <v>91220</v>
       </c>
       <c r="G18" s="0">
-        <v>0</v>
+        <v>3.8999999999999999</v>
       </c>
       <c r="H18" s="0">
-        <v>0</v>
+        <v>8.3800000000000008</v>
       </c>
       <c r="I18" s="0">
-        <v>88.459999999999994</v>
+        <v>85.840000000000003</v>
       </c>
       <c r="J18" s="0">
-        <v>1563</v>
+        <v>762</v>
       </c>
       <c r="K18" s="0">
-        <v>4757.8400000000001</v>
+        <v>4105.46</v>
       </c>
       <c r="L18" s="0">
-        <v>21.350000000000001</v>
+        <v>25.890000000000001</v>
       </c>
       <c r="M18" s="0">
-        <v>0.050999999999999997</v>
+        <v>0.072999999999999995</v>
       </c>
     </row>
     <row r="19">
@@ -939,40 +966,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>42078717441</v>
+        <v>9447223831</v>
       </c>
       <c r="C19" s="0">
-        <v>51645275069</v>
+        <v>11364192983</v>
       </c>
       <c r="D19" s="0">
-        <v>0</v>
+        <v>284318</v>
       </c>
       <c r="E19" s="0">
-        <v>215</v>
+        <v>115</v>
       </c>
       <c r="F19" s="0">
-        <v>72968</v>
+        <v>225245</v>
       </c>
       <c r="G19" s="0">
-        <v>0</v>
+        <v>5.6399999999999997</v>
       </c>
       <c r="H19" s="0">
-        <v>0</v>
+        <v>8.5099999999999998</v>
       </c>
       <c r="I19" s="0">
-        <v>81.480000000000004</v>
+        <v>83.129999999999995</v>
       </c>
       <c r="J19" s="0">
-        <v>3321</v>
+        <v>452</v>
       </c>
       <c r="K19" s="0">
-        <v>6186.2600000000002</v>
+        <v>3759.0700000000002</v>
       </c>
       <c r="L19" s="0">
-        <v>29.010000000000002</v>
+        <v>33.409999999999997</v>
       </c>
       <c r="M19" s="0">
-        <v>0.062</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="20">
@@ -980,40 +1007,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>15789309805</v>
+        <v>6483761108</v>
       </c>
       <c r="C20" s="0">
-        <v>19340224456</v>
+        <v>8027698589</v>
       </c>
       <c r="D20" s="0">
-        <v>1441149</v>
+        <v>396625</v>
       </c>
       <c r="E20" s="0">
-        <v>244</v>
+        <v>143</v>
       </c>
       <c r="F20" s="0">
-        <v>20747</v>
+        <v>98496</v>
       </c>
       <c r="G20" s="0">
-        <v>1.55</v>
+        <v>4.8700000000000001</v>
       </c>
       <c r="H20" s="0">
-        <v>12.390000000000001</v>
+        <v>8.3499999999999996</v>
       </c>
       <c r="I20" s="0">
-        <v>81.640000000000001</v>
+        <v>80.769999999999996</v>
       </c>
       <c r="J20" s="0">
-        <v>3827</v>
+        <v>571</v>
       </c>
       <c r="K20" s="0">
-        <v>6269.6899999999996</v>
+        <v>4021.4699999999998</v>
       </c>
       <c r="L20" s="0">
-        <v>25.739999999999998</v>
+        <v>28.190000000000001</v>
       </c>
       <c r="M20" s="0">
-        <v>0.053999999999999999</v>
+        <v>0.085000000000000006</v>
       </c>
     </row>
     <row r="21">
@@ -1021,40 +1048,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>23361124561</v>
+        <v>896566555</v>
       </c>
       <c r="C21" s="0">
-        <v>28078529663</v>
+        <v>1292099328</v>
       </c>
       <c r="D21" s="0">
-        <v>1564263</v>
+        <v>365000</v>
       </c>
       <c r="E21" s="0">
-        <v>267</v>
+        <v>123</v>
       </c>
       <c r="F21" s="0">
-        <v>30774</v>
+        <v>17682</v>
       </c>
       <c r="G21" s="0">
-        <v>1.71</v>
+        <v>4.9900000000000002</v>
       </c>
       <c r="H21" s="0">
-        <v>12.630000000000001</v>
+        <v>8.3599999999999994</v>
       </c>
       <c r="I21" s="0">
-        <v>83.200000000000003</v>
+        <v>69.390000000000001</v>
       </c>
       <c r="J21" s="0">
-        <v>3467</v>
+        <v>569</v>
       </c>
       <c r="K21" s="0">
-        <v>7077.04</v>
+        <v>3072.98</v>
       </c>
       <c r="L21" s="0">
-        <v>26.850000000000001</v>
+        <v>23.940000000000001</v>
       </c>
       <c r="M21" s="0">
-        <v>0.057000000000000002</v>
+        <v>0.070000000000000007</v>
       </c>
     </row>
     <row r="22">
@@ -1062,40 +1089,40 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>22820707926</v>
+        <v>91161376592</v>
       </c>
       <c r="C22" s="0">
-        <v>26713192336</v>
+        <v>109381505540</v>
       </c>
       <c r="D22" s="0">
-        <v>1856372</v>
+        <v>531468</v>
       </c>
       <c r="E22" s="0">
-        <v>291</v>
+        <v>141</v>
       </c>
       <c r="F22" s="0">
-        <v>23099</v>
+        <v>1076832</v>
       </c>
       <c r="G22" s="0">
-        <v>1.6100000000000001</v>
+        <v>5.2300000000000004</v>
       </c>
       <c r="H22" s="0">
-        <v>13.289999999999999</v>
+        <v>10.42</v>
       </c>
       <c r="I22" s="0">
-        <v>85.430000000000007</v>
+        <v>83.340000000000003</v>
       </c>
       <c r="J22" s="0">
-        <v>3968</v>
+        <v>721</v>
       </c>
       <c r="K22" s="0">
-        <v>6957.0799999999999</v>
+        <v>3592.1900000000001</v>
       </c>
       <c r="L22" s="0">
-        <v>23.870000000000001</v>
+        <v>25.489999999999998</v>
       </c>
       <c r="M22" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.070000000000000007</v>
       </c>
     </row>
     <row r="23">
@@ -1103,40 +1130,40 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>299725643</v>
+        <v>153937603405</v>
       </c>
       <c r="C23" s="0">
-        <v>329828276</v>
+        <v>181548105057</v>
       </c>
       <c r="D23" s="0">
-        <v>845714</v>
+        <v>664476</v>
       </c>
       <c r="E23" s="0">
-        <v>306</v>
+        <v>165</v>
       </c>
       <c r="F23" s="0">
-        <v>168</v>
+        <v>962368</v>
       </c>
       <c r="G23" s="0">
-        <v>0.42999999999999999</v>
+        <v>3.52</v>
       </c>
       <c r="H23" s="0">
-        <v>5.46</v>
+        <v>10.380000000000001</v>
       </c>
       <c r="I23" s="0">
-        <v>90.870000000000005</v>
+        <v>84.790000000000006</v>
       </c>
       <c r="J23" s="0">
-        <v>6423</v>
+        <v>1147</v>
       </c>
       <c r="K23" s="0">
-        <v>7624.1800000000003</v>
+        <v>3704.4499999999998</v>
       </c>
       <c r="L23" s="0">
-        <v>24.940000000000001</v>
+        <v>22.530000000000001</v>
       </c>
       <c r="M23" s="0">
-        <v>0.049000000000000002</v>
+        <v>0.058000000000000003</v>
       </c>
     </row>
     <row r="24">
@@ -1144,40 +1171,40 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>13341449274</v>
+        <v>38900540444</v>
       </c>
       <c r="C24" s="0">
-        <v>16605195881</v>
+        <v>45040396519</v>
       </c>
       <c r="D24" s="0">
-        <v>1442676</v>
+        <v>771108</v>
       </c>
       <c r="E24" s="0">
-        <v>223</v>
+        <v>179</v>
       </c>
       <c r="F24" s="0">
-        <v>14888</v>
+        <v>204022</v>
       </c>
       <c r="G24" s="0">
-        <v>1.29</v>
+        <v>3.4900000000000002</v>
       </c>
       <c r="H24" s="0">
-        <v>12.890000000000001</v>
+        <v>10.91</v>
       </c>
       <c r="I24" s="0">
-        <v>80.349999999999994</v>
+        <v>86.370000000000005</v>
       </c>
       <c r="J24" s="0">
-        <v>5004</v>
+        <v>1235</v>
       </c>
       <c r="K24" s="0">
-        <v>7234.9700000000003</v>
+        <v>3535.4699999999998</v>
       </c>
       <c r="L24" s="0">
-        <v>32.460000000000001</v>
+        <v>19.780000000000001</v>
       </c>
       <c r="M24" s="0">
-        <v>0.065000000000000002</v>
+        <v>0.050000000000000003</v>
       </c>
     </row>
     <row r="25">
@@ -1185,40 +1212,40 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
-        <v>15262415406</v>
+        <v>36360150286</v>
       </c>
       <c r="C25" s="0">
-        <v>19194311381</v>
+        <v>41662915500</v>
       </c>
       <c r="D25" s="0">
-        <v>1788845</v>
+        <v>825172</v>
       </c>
       <c r="E25" s="0">
-        <v>262</v>
+        <v>180</v>
       </c>
       <c r="F25" s="0">
-        <v>12837</v>
+        <v>179953</v>
       </c>
       <c r="G25" s="0">
-        <v>1.2</v>
+        <v>3.5600000000000001</v>
       </c>
       <c r="H25" s="0">
-        <v>13.35</v>
+        <v>11.449999999999999</v>
       </c>
       <c r="I25" s="0">
-        <v>79.519999999999996</v>
+        <v>87.269999999999996</v>
       </c>
       <c r="J25" s="0">
-        <v>5732</v>
+        <v>1289</v>
       </c>
       <c r="K25" s="0">
-        <v>7371.5699999999997</v>
+        <v>3508.29</v>
       </c>
       <c r="L25" s="0">
-        <v>28.25</v>
+        <v>19.530000000000001</v>
       </c>
       <c r="M25" s="0">
-        <v>0.055</v>
+        <v>0.049000000000000002</v>
       </c>
     </row>
     <row r="26">
@@ -1226,37 +1253,37 @@
         <v>25</v>
       </c>
       <c r="B26" s="0">
-        <v>68915028524</v>
+        <v>49455164252</v>
       </c>
       <c r="C26" s="0">
-        <v>84766010508</v>
+        <v>57527592939</v>
       </c>
       <c r="D26" s="0">
-        <v>1672903</v>
+        <v>774261</v>
       </c>
       <c r="E26" s="0">
-        <v>290</v>
+        <v>180</v>
       </c>
       <c r="F26" s="0">
-        <v>66934</v>
+        <v>182494</v>
       </c>
       <c r="G26" s="0">
-        <v>1.3200000000000001</v>
+        <v>2.46</v>
       </c>
       <c r="H26" s="0">
-        <v>11.93</v>
+        <v>10.26</v>
       </c>
       <c r="I26" s="0">
-        <v>81.299999999999997</v>
+        <v>85.969999999999999</v>
       </c>
       <c r="J26" s="0">
-        <v>4476</v>
+        <v>1770</v>
       </c>
       <c r="K26" s="0">
-        <v>8755.1900000000005</v>
+        <v>4666.8900000000003</v>
       </c>
       <c r="L26" s="0">
-        <v>30.890000000000001</v>
+        <v>26.18</v>
       </c>
       <c r="M26" s="0">
         <v>0.062</v>
@@ -1267,40 +1294,40 @@
         <v>26</v>
       </c>
       <c r="B27" s="0">
-        <v>16472096294</v>
+        <v>11098385803</v>
       </c>
       <c r="C27" s="0">
-        <v>20885405745</v>
+        <v>12545747746</v>
       </c>
       <c r="D27" s="0">
-        <v>1864768</v>
+        <v>0</v>
       </c>
       <c r="E27" s="0">
-        <v>325</v>
+        <v>223</v>
       </c>
       <c r="F27" s="0">
-        <v>12753</v>
+        <v>36005</v>
       </c>
       <c r="G27" s="0">
-        <v>1.1399999999999999</v>
+        <v>0</v>
       </c>
       <c r="H27" s="0">
-        <v>11.48</v>
+        <v>0</v>
       </c>
       <c r="I27" s="0">
-        <v>78.870000000000005</v>
+        <v>88.459999999999994</v>
       </c>
       <c r="J27" s="0">
-        <v>5037</v>
+        <v>1563</v>
       </c>
       <c r="K27" s="0">
-        <v>10262.379999999999</v>
+        <v>4757.8400000000001</v>
       </c>
       <c r="L27" s="0">
-        <v>31.579999999999998</v>
+        <v>21.350000000000001</v>
       </c>
       <c r="M27" s="0">
-        <v>0.063</v>
+        <v>0.050999999999999997</v>
       </c>
     </row>
     <row r="28">
@@ -1308,40 +1335,409 @@
         <v>27</v>
       </c>
       <c r="B28" s="0">
-        <v>882746567069</v>
+        <v>42078717441</v>
       </c>
       <c r="C28" s="0">
-        <v>1055345310552</v>
+        <v>51645275069</v>
       </c>
       <c r="D28" s="0">
         <v>0</v>
       </c>
       <c r="E28" s="0">
+        <v>215</v>
+      </c>
+      <c r="F28" s="0">
+        <v>72968</v>
+      </c>
+      <c r="G28" s="0">
+        <v>0</v>
+      </c>
+      <c r="H28" s="0">
+        <v>0</v>
+      </c>
+      <c r="I28" s="0">
+        <v>81.480000000000004</v>
+      </c>
+      <c r="J28" s="0">
+        <v>3321</v>
+      </c>
+      <c r="K28" s="0">
+        <v>6186.2600000000002</v>
+      </c>
+      <c r="L28" s="0">
+        <v>29.010000000000002</v>
+      </c>
+      <c r="M28" s="0">
+        <v>0.062</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="0">
+        <v>15789309805</v>
+      </c>
+      <c r="C29" s="0">
+        <v>19340224456</v>
+      </c>
+      <c r="D29" s="0">
+        <v>1441149</v>
+      </c>
+      <c r="E29" s="0">
+        <v>244</v>
+      </c>
+      <c r="F29" s="0">
+        <v>20747</v>
+      </c>
+      <c r="G29" s="0">
+        <v>1.55</v>
+      </c>
+      <c r="H29" s="0">
+        <v>12.390000000000001</v>
+      </c>
+      <c r="I29" s="0">
+        <v>81.640000000000001</v>
+      </c>
+      <c r="J29" s="0">
+        <v>3827</v>
+      </c>
+      <c r="K29" s="0">
+        <v>6269.6899999999996</v>
+      </c>
+      <c r="L29" s="0">
+        <v>25.739999999999998</v>
+      </c>
+      <c r="M29" s="0">
+        <v>0.053999999999999999</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="0">
+        <v>23361124561</v>
+      </c>
+      <c r="C30" s="0">
+        <v>28078529663</v>
+      </c>
+      <c r="D30" s="0">
+        <v>1564263</v>
+      </c>
+      <c r="E30" s="0">
+        <v>267</v>
+      </c>
+      <c r="F30" s="0">
+        <v>30774</v>
+      </c>
+      <c r="G30" s="0">
+        <v>1.71</v>
+      </c>
+      <c r="H30" s="0">
+        <v>12.630000000000001</v>
+      </c>
+      <c r="I30" s="0">
+        <v>83.200000000000003</v>
+      </c>
+      <c r="J30" s="0">
+        <v>3467</v>
+      </c>
+      <c r="K30" s="0">
+        <v>7077.04</v>
+      </c>
+      <c r="L30" s="0">
+        <v>26.850000000000001</v>
+      </c>
+      <c r="M30" s="0">
+        <v>0.057000000000000002</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="0">
+        <v>22820707926</v>
+      </c>
+      <c r="C31" s="0">
+        <v>26713192336</v>
+      </c>
+      <c r="D31" s="0">
+        <v>1856372</v>
+      </c>
+      <c r="E31" s="0">
+        <v>291</v>
+      </c>
+      <c r="F31" s="0">
+        <v>23099</v>
+      </c>
+      <c r="G31" s="0">
+        <v>1.6100000000000001</v>
+      </c>
+      <c r="H31" s="0">
+        <v>13.289999999999999</v>
+      </c>
+      <c r="I31" s="0">
+        <v>85.430000000000007</v>
+      </c>
+      <c r="J31" s="0">
+        <v>3968</v>
+      </c>
+      <c r="K31" s="0">
+        <v>6957.0799999999999</v>
+      </c>
+      <c r="L31" s="0">
+        <v>23.870000000000001</v>
+      </c>
+      <c r="M31" s="0">
+        <v>0.050000000000000003</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="0">
+        <v>299725643</v>
+      </c>
+      <c r="C32" s="0">
+        <v>329828276</v>
+      </c>
+      <c r="D32" s="0">
+        <v>845714</v>
+      </c>
+      <c r="E32" s="0">
+        <v>306</v>
+      </c>
+      <c r="F32" s="0">
+        <v>168</v>
+      </c>
+      <c r="G32" s="0">
+        <v>0.42999999999999999</v>
+      </c>
+      <c r="H32" s="0">
+        <v>5.46</v>
+      </c>
+      <c r="I32" s="0">
+        <v>90.870000000000005</v>
+      </c>
+      <c r="J32" s="0">
+        <v>6423</v>
+      </c>
+      <c r="K32" s="0">
+        <v>7624.1800000000003</v>
+      </c>
+      <c r="L32" s="0">
+        <v>24.940000000000001</v>
+      </c>
+      <c r="M32" s="0">
+        <v>0.049000000000000002</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="0">
+        <v>13341449274</v>
+      </c>
+      <c r="C33" s="0">
+        <v>16605195881</v>
+      </c>
+      <c r="D33" s="0">
+        <v>1442676</v>
+      </c>
+      <c r="E33" s="0">
+        <v>223</v>
+      </c>
+      <c r="F33" s="0">
+        <v>14888</v>
+      </c>
+      <c r="G33" s="0">
+        <v>1.29</v>
+      </c>
+      <c r="H33" s="0">
+        <v>12.890000000000001</v>
+      </c>
+      <c r="I33" s="0">
+        <v>80.349999999999994</v>
+      </c>
+      <c r="J33" s="0">
+        <v>5004</v>
+      </c>
+      <c r="K33" s="0">
+        <v>7234.9700000000003</v>
+      </c>
+      <c r="L33" s="0">
+        <v>32.460000000000001</v>
+      </c>
+      <c r="M33" s="0">
+        <v>0.065000000000000002</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="0">
+        <v>15262415406</v>
+      </c>
+      <c r="C34" s="0">
+        <v>19194311381</v>
+      </c>
+      <c r="D34" s="0">
+        <v>1788845</v>
+      </c>
+      <c r="E34" s="0">
+        <v>262</v>
+      </c>
+      <c r="F34" s="0">
+        <v>12837</v>
+      </c>
+      <c r="G34" s="0">
+        <v>1.2</v>
+      </c>
+      <c r="H34" s="0">
+        <v>13.35</v>
+      </c>
+      <c r="I34" s="0">
+        <v>79.519999999999996</v>
+      </c>
+      <c r="J34" s="0">
+        <v>5732</v>
+      </c>
+      <c r="K34" s="0">
+        <v>7371.5699999999997</v>
+      </c>
+      <c r="L34" s="0">
+        <v>28.25</v>
+      </c>
+      <c r="M34" s="0">
+        <v>0.055</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="0">
+        <v>68915028524</v>
+      </c>
+      <c r="C35" s="0">
+        <v>84766010508</v>
+      </c>
+      <c r="D35" s="0">
+        <v>1672903</v>
+      </c>
+      <c r="E35" s="0">
+        <v>290</v>
+      </c>
+      <c r="F35" s="0">
+        <v>66934</v>
+      </c>
+      <c r="G35" s="0">
+        <v>1.3200000000000001</v>
+      </c>
+      <c r="H35" s="0">
+        <v>11.93</v>
+      </c>
+      <c r="I35" s="0">
+        <v>81.299999999999997</v>
+      </c>
+      <c r="J35" s="0">
+        <v>4476</v>
+      </c>
+      <c r="K35" s="0">
+        <v>8755.1900000000005</v>
+      </c>
+      <c r="L35" s="0">
+        <v>30.890000000000001</v>
+      </c>
+      <c r="M35" s="0">
+        <v>0.062</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" s="0">
+        <v>16472096294</v>
+      </c>
+      <c r="C36" s="0">
+        <v>20885405745</v>
+      </c>
+      <c r="D36" s="0">
+        <v>1864768</v>
+      </c>
+      <c r="E36" s="0">
+        <v>325</v>
+      </c>
+      <c r="F36" s="0">
+        <v>12753</v>
+      </c>
+      <c r="G36" s="0">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="H36" s="0">
+        <v>11.48</v>
+      </c>
+      <c r="I36" s="0">
+        <v>78.870000000000005</v>
+      </c>
+      <c r="J36" s="0">
+        <v>5037</v>
+      </c>
+      <c r="K36" s="0">
+        <v>10262.379999999999</v>
+      </c>
+      <c r="L36" s="0">
+        <v>31.579999999999998</v>
+      </c>
+      <c r="M36" s="0">
+        <v>0.063</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="0">
+        <v>925512391488</v>
+      </c>
+      <c r="C37" s="0">
+        <v>1106877914866</v>
+      </c>
+      <c r="D37" s="0">
+        <v>0</v>
+      </c>
+      <c r="E37" s="0">
         <v>131</v>
       </c>
-      <c r="F28" s="0">
-        <v>6897535</v>
-      </c>
-      <c r="G28" s="0">
-        <v>0</v>
-      </c>
-      <c r="H28" s="0">
-        <v>0</v>
-      </c>
-      <c r="I28" s="0">
-        <v>83.650000000000006</v>
-      </c>
-      <c r="J28" s="0">
-        <v>951</v>
-      </c>
-      <c r="K28" s="0">
-        <v>3680.21</v>
-      </c>
-      <c r="L28" s="0">
-        <v>24.260000000000002</v>
-      </c>
-      <c r="M28" s="0">
-        <v>0.060999999999999999</v>
+      <c r="F37" s="0">
+        <v>7611722</v>
+      </c>
+      <c r="G37" s="0">
+        <v>0</v>
+      </c>
+      <c r="H37" s="0">
+        <v>0</v>
+      </c>
+      <c r="I37" s="0">
+        <v>83.609999999999999</v>
+      </c>
+      <c r="J37" s="0">
+        <v>910</v>
+      </c>
+      <c r="K37" s="0">
+        <v>3665.4899999999998</v>
+      </c>
+      <c r="L37" s="0">
+        <v>24.359999999999999</v>
+      </c>
+      <c r="M37" s="0">
+        <v>0.062</v>
       </c>
     </row>
   </sheetData>
